--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T08:27:54+00:00</t>
+    <t>2023-04-26T14:43:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T14:43:04+00:00</t>
+    <t>2023-04-27T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T16:49:23+00:00</t>
+    <t>2023-05-02T12:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T12:59:07+00:00</t>
+    <t>2023-05-02T13:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T13:06:55+00:00</t>
+    <t>2023-05-02T14:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:33:57+00:00</t>
+    <t>2023-07-18T09:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:12+00:00</t>
+    <t>2023-07-18T09:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:49+00:00</t>
+    <t>2023-07-18T09:37:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4871" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4870" uniqueCount="662">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:37:51+00:00</t>
+    <t>2023-09-19T16:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -143,6 +143,10 @@
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
   </si>
   <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present. {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
+  </si>
+  <si>
     <t>Event</t>
   </si>
   <si>
@@ -552,7 +556,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -639,7 +643,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -1108,7 +1112,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1166,7 +1170,7 @@
     <t>Often just a dateTime for Vital Signs.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -1201,7 +1205,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -1251,7 +1255,7 @@
     <t>Vital Signs value are recorded using the Quantity data type. For supporting observations such as Cuff size could use other datatypes such as CodeableConcept.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>9. SHALL contain exactly one [1..1] value with @xsi:type="PQ" (CONF:7305).</t>
@@ -1531,10 +1535,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://www.interopsante.org/fhir/structuredefinition/observation/fr-obervation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1584,7 +1585,7 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J151-BodySiteBodyTemperature-ENS/FHIR/JDV-J151-BodySiteBodyTemperature-ENS</t>
@@ -1953,7 +1954,7 @@
     <t>Used when reporting vital signs panel components.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1975,7 +1976,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1987,7 +1988,7 @@
     <t>Used when reporting systolic and diastolic blood pressure.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
@@ -2044,7 +2045,7 @@
     <t>Vital Sign Value recorded with UCUM.</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Common UCUM units for recording Vital Signs.</t>
@@ -2080,7 +2081,7 @@
     <t>Observation.component.interpretation</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -2538,19 +2539,19 @@
         <v>36</v>
       </c>
       <c r="AJ1" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="AK1" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AL1" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AM1" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AN1" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AO1" t="s" s="2">
         <v>36</v>
@@ -2561,10 +2562,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2575,7 +2576,7 @@
         <v>34</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>36</v>
@@ -2584,19 +2585,19 @@
         <v>36</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2646,13 +2647,13 @@
         <v>36</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>36</v>
@@ -2681,10 +2682,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2695,7 +2696,7 @@
         <v>34</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>36</v>
@@ -2704,16 +2705,16 @@
         <v>36</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -2764,19 +2765,19 @@
         <v>36</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="s" s="2">
         <v>36</v>
@@ -2788,7 +2789,7 @@
         <v>36</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO3" t="s" s="2">
         <v>36</v>
@@ -2799,10 +2800,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2813,7 +2814,7 @@
         <v>34</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>36</v>
@@ -2825,13 +2826,13 @@
         <v>36</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2882,13 +2883,13 @@
         <v>36</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>36</v>
@@ -2906,7 +2907,7 @@
         <v>36</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>36</v>
@@ -2917,14 +2918,14 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
@@ -2943,16 +2944,16 @@
         <v>36</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2990,19 +2991,19 @@
         <v>36</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>34</v>
@@ -3011,10 +3012,10 @@
         <v>35</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>36</v>
@@ -3026,7 +3027,7 @@
         <v>36</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>36</v>
@@ -3037,10 +3038,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -3051,7 +3052,7 @@
         <v>34</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>36</v>
@@ -3060,19 +3061,19 @@
         <v>36</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3122,19 +3123,19 @@
         <v>36</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>36</v>
@@ -3146,7 +3147,7 @@
         <v>36</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>36</v>
@@ -3157,10 +3158,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3171,7 +3172,7 @@
         <v>34</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>36</v>
@@ -3180,19 +3181,19 @@
         <v>36</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3242,19 +3243,19 @@
         <v>36</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>36</v>
@@ -3266,7 +3267,7 @@
         <v>36</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>36</v>
@@ -3277,10 +3278,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -3291,7 +3292,7 @@
         <v>34</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>36</v>
@@ -3300,19 +3301,19 @@
         <v>36</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3362,19 +3363,19 @@
         <v>36</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>36</v>
@@ -3386,7 +3387,7 @@
         <v>36</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>36</v>
@@ -3397,10 +3398,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3420,19 +3421,19 @@
         <v>36</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3482,7 +3483,7 @@
         <v>36</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>34</v>
@@ -3491,10 +3492,10 @@
         <v>35</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>36</v>
@@ -3506,7 +3507,7 @@
         <v>36</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>36</v>
@@ -3517,10 +3518,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3540,19 +3541,19 @@
         <v>36</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3578,13 +3579,13 @@
         <v>36</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>36</v>
@@ -3602,7 +3603,7 @@
         <v>36</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>34</v>
@@ -3611,10 +3612,10 @@
         <v>35</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>36</v>
@@ -3623,10 +3624,10 @@
         <v>36</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>36</v>
@@ -3637,10 +3638,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3660,19 +3661,19 @@
         <v>36</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3698,13 +3699,13 @@
         <v>36</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>36</v>
@@ -3722,7 +3723,7 @@
         <v>36</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>34</v>
@@ -3731,10 +3732,10 @@
         <v>35</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>36</v>
@@ -3743,10 +3744,10 @@
         <v>36</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>36</v>
@@ -3757,10 +3758,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3771,28 +3772,28 @@
         <v>34</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3842,19 +3843,19 @@
         <v>36</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>36</v>
@@ -3866,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>36</v>
@@ -3877,10 +3878,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3891,7 +3892,7 @@
         <v>34</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>36</v>
@@ -3903,16 +3904,16 @@
         <v>36</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3938,13 +3939,13 @@
         <v>36</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>36</v>
@@ -3962,19 +3963,19 @@
         <v>36</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>36</v>
@@ -3986,7 +3987,7 @@
         <v>36</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>36</v>
@@ -3997,21 +3998,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>36</v>
@@ -4023,16 +4024,16 @@
         <v>36</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4082,19 +4083,19 @@
         <v>36</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>36</v>
@@ -4106,7 +4107,7 @@
         <v>36</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>36</v>
@@ -4117,14 +4118,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4143,16 +4144,16 @@
         <v>36</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4202,7 +4203,7 @@
         <v>36</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>34</v>
@@ -4226,7 +4227,7 @@
         <v>36</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>36</v>
@@ -4237,14 +4238,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4263,16 +4264,16 @@
         <v>36</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4310,19 +4311,19 @@
         <v>36</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>34</v>
@@ -4331,10 +4332,10 @@
         <v>35</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>36</v>
@@ -4346,7 +4347,7 @@
         <v>36</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>36</v>
@@ -4357,13 +4358,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>36</v>
@@ -4373,7 +4374,7 @@
         <v>34</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>36</v>
@@ -4385,13 +4386,13 @@
         <v>36</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4442,7 +4443,7 @@
         <v>36</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>34</v>
@@ -4451,10 +4452,10 @@
         <v>35</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>36</v>
@@ -4466,7 +4467,7 @@
         <v>36</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>36</v>
@@ -4477,26 +4478,26 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>36</v>
@@ -4505,16 +4506,16 @@
         <v>36</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4564,7 +4565,7 @@
         <v>36</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>34</v>
@@ -4573,10 +4574,10 @@
         <v>35</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>36</v>
@@ -4588,7 +4589,7 @@
         <v>36</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>36</v>
@@ -4599,13 +4600,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>36</v>
@@ -4615,7 +4616,7 @@
         <v>34</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>36</v>
@@ -4627,13 +4628,13 @@
         <v>36</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4684,7 +4685,7 @@
         <v>36</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>34</v>
@@ -4693,10 +4694,10 @@
         <v>35</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>36</v>
@@ -4719,14 +4720,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4739,25 +4740,25 @@
         <v>36</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>36</v>
@@ -4794,19 +4795,19 @@
         <v>36</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>34</v>
@@ -4815,10 +4816,10 @@
         <v>35</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>36</v>
@@ -4830,7 +4831,7 @@
         <v>36</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>36</v>
@@ -4841,10 +4842,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4864,20 +4865,20 @@
         <v>36</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>36</v>
@@ -4926,7 +4927,7 @@
         <v>36</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>34</v>
@@ -4935,25 +4936,25 @@
         <v>35</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>36</v>
@@ -4961,14 +4962,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4984,22 +4985,22 @@
         <v>36</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>36</v>
@@ -5048,7 +5049,7 @@
         <v>36</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>34</v>
@@ -5057,22 +5058,22 @@
         <v>35</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>36</v>
@@ -5083,14 +5084,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5106,19 +5107,19 @@
         <v>36</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5168,7 +5169,7 @@
         <v>36</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>34</v>
@@ -5177,22 +5178,22 @@
         <v>35</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>36</v>
@@ -5203,10 +5204,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5214,34 +5215,34 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>36</v>
@@ -5266,13 +5267,13 @@
         <v>36</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>36</v>
@@ -5290,34 +5291,34 @@
         <v>36</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>36</v>
@@ -5325,10 +5326,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5336,13 +5337,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>36</v>
@@ -5351,19 +5352,19 @@
         <v>36</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>36</v>
@@ -5388,29 +5389,29 @@
         <v>36</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>34</v>
@@ -5419,10 +5420,10 @@
         <v>35</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>36</v>
@@ -5431,13 +5432,13 @@
         <v>36</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>36</v>
@@ -5445,26 +5446,26 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>36</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>36</v>
@@ -5473,19 +5474,19 @@
         <v>36</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>36</v>
@@ -5510,13 +5511,13 @@
         <v>36</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>36</v>
@@ -5534,7 +5535,7 @@
         <v>36</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>34</v>
@@ -5543,10 +5544,10 @@
         <v>35</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>36</v>
@@ -5555,13 +5556,13 @@
         <v>36</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>36</v>
@@ -5569,10 +5570,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5583,7 +5584,7 @@
         <v>34</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>36</v>
@@ -5595,13 +5596,13 @@
         <v>36</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5652,13 +5653,13 @@
         <v>36</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>36</v>
@@ -5676,7 +5677,7 @@
         <v>36</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>36</v>
@@ -5687,14 +5688,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5713,16 +5714,16 @@
         <v>36</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5760,19 +5761,19 @@
         <v>36</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>34</v>
@@ -5781,10 +5782,10 @@
         <v>35</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>36</v>
@@ -5796,7 +5797,7 @@
         <v>36</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>36</v>
@@ -5807,10 +5808,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5818,34 +5819,34 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>36</v>
@@ -5894,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>34</v>
@@ -5903,10 +5904,10 @@
         <v>35</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>36</v>
@@ -5915,10 +5916,10 @@
         <v>36</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>36</v>
@@ -5929,10 +5930,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5943,7 +5944,7 @@
         <v>34</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>36</v>
@@ -5955,13 +5956,13 @@
         <v>36</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6012,13 +6013,13 @@
         <v>36</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>36</v>
@@ -6036,7 +6037,7 @@
         <v>36</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>36</v>
@@ -6047,14 +6048,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6073,16 +6074,16 @@
         <v>36</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6120,19 +6121,19 @@
         <v>36</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>34</v>
@@ -6141,10 +6142,10 @@
         <v>35</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>36</v>
@@ -6156,7 +6157,7 @@
         <v>36</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>36</v>
@@ -6167,10 +6168,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6178,41 +6179,41 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>36</v>
@@ -6254,19 +6255,19 @@
         <v>36</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>36</v>
@@ -6275,10 +6276,10 @@
         <v>36</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>36</v>
@@ -6289,10 +6290,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6303,7 +6304,7 @@
         <v>34</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>36</v>
@@ -6312,19 +6313,19 @@
         <v>36</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6374,19 +6375,19 @@
         <v>36</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>36</v>
@@ -6395,10 +6396,10 @@
         <v>36</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>36</v>
@@ -6409,10 +6410,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6420,41 +6421,41 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>36</v>
@@ -6496,19 +6497,19 @@
         <v>36</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>36</v>
@@ -6517,10 +6518,10 @@
         <v>36</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>36</v>
@@ -6531,10 +6532,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6545,7 +6546,7 @@
         <v>34</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>36</v>
@@ -6554,22 +6555,22 @@
         <v>36</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>36</v>
@@ -6618,19 +6619,19 @@
         <v>36</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>36</v>
@@ -6639,10 +6640,10 @@
         <v>36</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>36</v>
@@ -6653,10 +6654,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6667,7 +6668,7 @@
         <v>34</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>36</v>
@@ -6676,22 +6677,22 @@
         <v>36</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>36</v>
@@ -6740,19 +6741,19 @@
         <v>36</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>36</v>
@@ -6761,10 +6762,10 @@
         <v>36</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>36</v>
@@ -6775,10 +6776,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6789,7 +6790,7 @@
         <v>34</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>36</v>
@@ -6798,22 +6799,22 @@
         <v>36</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>36</v>
@@ -6862,19 +6863,19 @@
         <v>36</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>36</v>
@@ -6883,10 +6884,10 @@
         <v>36</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>36</v>
@@ -6897,45 +6898,45 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>36</v>
@@ -6960,13 +6961,13 @@
         <v>36</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>36</v>
@@ -6984,45 +6985,45 @@
         <v>36</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7033,7 +7034,7 @@
         <v>34</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>36</v>
@@ -7045,13 +7046,13 @@
         <v>36</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7102,13 +7103,13 @@
         <v>36</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>36</v>
@@ -7126,7 +7127,7 @@
         <v>36</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>36</v>
@@ -7137,14 +7138,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7163,16 +7164,16 @@
         <v>36</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7210,19 +7211,19 @@
         <v>36</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>34</v>
@@ -7231,10 +7232,10 @@
         <v>35</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>36</v>
@@ -7246,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>36</v>
@@ -7257,10 +7258,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7280,22 +7281,22 @@
         <v>36</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>36</v>
@@ -7332,17 +7333,17 @@
         <v>36</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>34</v>
@@ -7351,10 +7352,10 @@
         <v>35</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>36</v>
@@ -7363,10 +7364,10 @@
         <v>36</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>36</v>
@@ -7377,23 +7378,23 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>36</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>36</v>
@@ -7402,22 +7403,22 @@
         <v>36</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>36</v>
@@ -7466,7 +7467,7 @@
         <v>36</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>34</v>
@@ -7475,10 +7476,10 @@
         <v>35</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>36</v>
@@ -7487,10 +7488,10 @@
         <v>36</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>36</v>
@@ -7501,10 +7502,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7515,7 +7516,7 @@
         <v>34</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>36</v>
@@ -7527,13 +7528,13 @@
         <v>36</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7584,13 +7585,13 @@
         <v>36</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>36</v>
@@ -7608,7 +7609,7 @@
         <v>36</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>36</v>
@@ -7619,14 +7620,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7645,16 +7646,16 @@
         <v>36</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7692,19 +7693,19 @@
         <v>36</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>34</v>
@@ -7713,10 +7714,10 @@
         <v>35</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>36</v>
@@ -7728,7 +7729,7 @@
         <v>36</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>36</v>
@@ -7739,10 +7740,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7750,10 +7751,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>36</v>
@@ -7762,29 +7763,29 @@
         <v>36</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>36</v>
@@ -7826,19 +7827,19 @@
         <v>36</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>36</v>
@@ -7847,10 +7848,10 @@
         <v>36</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>36</v>
@@ -7861,10 +7862,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7875,7 +7876,7 @@
         <v>34</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>36</v>
@@ -7884,19 +7885,19 @@
         <v>36</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7946,19 +7947,19 @@
         <v>36</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>36</v>
@@ -7967,10 +7968,10 @@
         <v>36</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>36</v>
@@ -7981,10 +7982,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7992,10 +7993,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>36</v>
@@ -8004,29 +8005,29 @@
         <v>36</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>36</v>
@@ -8068,19 +8069,19 @@
         <v>36</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>36</v>
@@ -8089,10 +8090,10 @@
         <v>36</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>36</v>
@@ -8103,10 +8104,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8117,7 +8118,7 @@
         <v>34</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>36</v>
@@ -8126,22 +8127,22 @@
         <v>36</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>36</v>
@@ -8190,19 +8191,19 @@
         <v>36</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>36</v>
@@ -8211,10 +8212,10 @@
         <v>36</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>36</v>
@@ -8225,10 +8226,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8239,7 +8240,7 @@
         <v>34</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>36</v>
@@ -8248,22 +8249,22 @@
         <v>36</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>36</v>
@@ -8312,19 +8313,19 @@
         <v>36</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>36</v>
@@ -8333,10 +8334,10 @@
         <v>36</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>36</v>
@@ -8347,10 +8348,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8361,7 +8362,7 @@
         <v>34</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>36</v>
@@ -8370,22 +8371,22 @@
         <v>36</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>36</v>
@@ -8434,19 +8435,19 @@
         <v>36</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>36</v>
@@ -8455,10 +8456,10 @@
         <v>36</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>36</v>
@@ -8469,10 +8470,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8480,34 +8481,34 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>36</v>
@@ -8556,34 +8557,34 @@
         <v>36</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>36</v>
@@ -8591,10 +8592,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8614,19 +8615,19 @@
         <v>36</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8676,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>34</v>
@@ -8685,10 +8686,10 @@
         <v>35</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>36</v>
@@ -8697,13 +8698,13 @@
         <v>36</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>36</v>
@@ -8711,21 +8712,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>36</v>
@@ -8734,22 +8735,22 @@
         <v>36</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>36</v>
@@ -8798,34 +8799,34 @@
         <v>36</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>36</v>
@@ -8833,45 +8834,45 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>36</v>
@@ -8920,34 +8921,34 @@
         <v>36</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>36</v>
@@ -8955,10 +8956,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8969,7 +8970,7 @@
         <v>34</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>36</v>
@@ -8978,19 +8979,19 @@
         <v>36</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9040,19 +9041,19 @@
         <v>36</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>36</v>
@@ -9061,13 +9062,13 @@
         <v>36</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>36</v>
@@ -9075,10 +9076,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9098,22 +9099,22 @@
         <v>36</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>36</v>
@@ -9162,7 +9163,7 @@
         <v>36</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>34</v>
@@ -9171,25 +9172,25 @@
         <v>35</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>36</v>
@@ -9197,10 +9198,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9211,31 +9212,31 @@
         <v>34</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>36</v>
@@ -9272,58 +9273,58 @@
         <v>36</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>36</v>
@@ -9333,31 +9334,31 @@
         <v>34</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>36</v>
@@ -9367,7 +9368,7 @@
         <v>36</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>36</v>
@@ -9406,45 +9407,45 @@
         <v>36</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9455,7 +9456,7 @@
         <v>34</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>36</v>
@@ -9467,13 +9468,13 @@
         <v>36</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9524,13 +9525,13 @@
         <v>36</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>36</v>
@@ -9548,7 +9549,7 @@
         <v>36</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>36</v>
@@ -9559,14 +9560,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9585,16 +9586,16 @@
         <v>36</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9632,19 +9633,19 @@
         <v>36</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>34</v>
@@ -9653,10 +9654,10 @@
         <v>35</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>36</v>
@@ -9668,7 +9669,7 @@
         <v>36</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>36</v>
@@ -9679,10 +9680,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9690,34 +9691,34 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>36</v>
@@ -9766,19 +9767,19 @@
         <v>36</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>36</v>
@@ -9787,10 +9788,10 @@
         <v>36</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>36</v>
@@ -9801,10 +9802,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9815,37 +9816,37 @@
         <v>34</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q62" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="R62" t="s" s="2">
         <v>36</v>
@@ -9866,13 +9867,13 @@
         <v>36</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>36</v>
@@ -9890,19 +9891,19 @@
         <v>36</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>36</v>
@@ -9911,10 +9912,10 @@
         <v>36</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>36</v>
@@ -9925,10 +9926,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9936,34 +9937,34 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>36</v>
@@ -10012,19 +10013,19 @@
         <v>36</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>36</v>
@@ -10033,10 +10034,10 @@
         <v>36</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>36</v>
@@ -10047,10 +10048,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10058,41 +10059,41 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>36</v>
@@ -10134,19 +10135,19 @@
         <v>36</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>36</v>
@@ -10155,10 +10156,10 @@
         <v>36</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>36</v>
@@ -10169,10 +10170,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10180,34 +10181,34 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>36</v>
@@ -10232,13 +10233,13 @@
         <v>36</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>36</v>
@@ -10256,19 +10257,19 @@
         <v>36</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>36</v>
@@ -10277,10 +10278,10 @@
         <v>36</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>36</v>
@@ -10291,10 +10292,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10305,10 +10306,10 @@
         <v>34</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>36</v>
@@ -10317,19 +10318,19 @@
         <v>36</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>36</v>
@@ -10354,13 +10355,13 @@
         <v>36</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>36</v>
@@ -10378,19 +10379,19 @@
         <v>36</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>36</v>
@@ -10399,10 +10400,10 @@
         <v>36</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>36</v>
@@ -10413,10 +10414,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10427,7 +10428,7 @@
         <v>34</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>36</v>
@@ -10439,13 +10440,13 @@
         <v>36</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10496,13 +10497,13 @@
         <v>36</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>36</v>
@@ -10520,7 +10521,7 @@
         <v>36</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>36</v>
@@ -10531,14 +10532,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10557,16 +10558,16 @@
         <v>36</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10604,19 +10605,19 @@
         <v>36</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>34</v>
@@ -10625,10 +10626,10 @@
         <v>35</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>36</v>
@@ -10640,7 +10641,7 @@
         <v>36</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>36</v>
@@ -10651,10 +10652,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10674,22 +10675,22 @@
         <v>36</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>36</v>
@@ -10738,7 +10739,7 @@
         <v>36</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>34</v>
@@ -10747,10 +10748,10 @@
         <v>35</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>36</v>
@@ -10759,10 +10760,10 @@
         <v>36</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>36</v>
@@ -10773,10 +10774,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10787,7 +10788,7 @@
         <v>34</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>36</v>
@@ -10799,13 +10800,13 @@
         <v>36</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10856,13 +10857,13 @@
         <v>36</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>36</v>
@@ -10880,7 +10881,7 @@
         <v>36</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>36</v>
@@ -10891,14 +10892,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10917,16 +10918,16 @@
         <v>36</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10964,19 +10965,19 @@
         <v>36</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>34</v>
@@ -10985,10 +10986,10 @@
         <v>35</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>36</v>
@@ -11000,7 +11001,7 @@
         <v>36</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>36</v>
@@ -11011,10 +11012,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11022,10 +11023,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>36</v>
@@ -11034,22 +11035,22 @@
         <v>36</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>36</v>
@@ -11098,19 +11099,19 @@
         <v>36</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>36</v>
@@ -11119,10 +11120,10 @@
         <v>36</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>36</v>
@@ -11133,10 +11134,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11147,7 +11148,7 @@
         <v>34</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>36</v>
@@ -11156,19 +11157,19 @@
         <v>36</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11218,19 +11219,19 @@
         <v>36</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>36</v>
@@ -11239,10 +11240,10 @@
         <v>36</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>36</v>
@@ -11253,10 +11254,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11264,10 +11265,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>36</v>
@@ -11276,22 +11277,22 @@
         <v>36</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>36</v>
@@ -11340,19 +11341,19 @@
         <v>36</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>36</v>
@@ -11361,10 +11362,10 @@
         <v>36</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>36</v>
@@ -11375,10 +11376,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11389,7 +11390,7 @@
         <v>34</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>36</v>
@@ -11398,22 +11399,22 @@
         <v>36</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>36</v>
@@ -11462,19 +11463,19 @@
         <v>36</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>36</v>
@@ -11483,10 +11484,10 @@
         <v>36</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>36</v>
@@ -11497,10 +11498,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11511,7 +11512,7 @@
         <v>34</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>36</v>
@@ -11520,22 +11521,22 @@
         <v>36</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>36</v>
@@ -11584,19 +11585,19 @@
         <v>36</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>36</v>
@@ -11605,10 +11606,10 @@
         <v>36</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>36</v>
@@ -11619,10 +11620,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11633,7 +11634,7 @@
         <v>34</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>36</v>
@@ -11642,22 +11643,22 @@
         <v>36</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>36</v>
@@ -11706,19 +11707,19 @@
         <v>36</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>36</v>
@@ -11727,10 +11728,10 @@
         <v>36</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>36</v>
@@ -11741,14 +11742,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11767,19 +11768,19 @@
         <v>36</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>36</v>
@@ -11804,11 +11805,9 @@
         <v>36</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
         <v>486</v>
       </c>
@@ -11828,7 +11827,7 @@
         <v>36</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>34</v>
@@ -11837,10 +11836,10 @@
         <v>35</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>36</v>
@@ -11959,10 +11958,10 @@
         <v>35</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>36</v>
@@ -11999,7 +11998,7 @@
         <v>34</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>36</v>
@@ -12011,7 +12010,7 @@
         <v>36</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>500</v>
@@ -12046,7 +12045,7 @@
         <v>36</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
@@ -12074,13 +12073,13 @@
         <v>34</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>36</v>
@@ -12117,7 +12116,7 @@
         <v>34</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>36</v>
@@ -12129,13 +12128,13 @@
         <v>36</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12186,13 +12185,13 @@
         <v>36</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>36</v>
@@ -12210,7 +12209,7 @@
         <v>36</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>36</v>
@@ -12228,7 +12227,7 @@
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12247,16 +12246,16 @@
         <v>36</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12294,19 +12293,19 @@
         <v>36</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>34</v>
@@ -12315,10 +12314,10 @@
         <v>35</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>36</v>
@@ -12330,7 +12329,7 @@
         <v>36</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>36</v>
@@ -12364,22 +12363,22 @@
         <v>36</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>36</v>
@@ -12428,7 +12427,7 @@
         <v>36</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>34</v>
@@ -12437,10 +12436,10 @@
         <v>35</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>36</v>
@@ -12449,10 +12448,10 @@
         <v>36</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>36</v>
@@ -12477,7 +12476,7 @@
         <v>34</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>36</v>
@@ -12489,13 +12488,13 @@
         <v>36</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12546,13 +12545,13 @@
         <v>36</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>36</v>
@@ -12570,7 +12569,7 @@
         <v>36</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>36</v>
@@ -12588,7 +12587,7 @@
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12607,16 +12606,16 @@
         <v>36</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12654,19 +12653,19 @@
         <v>36</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>34</v>
@@ -12675,10 +12674,10 @@
         <v>35</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>36</v>
@@ -12690,7 +12689,7 @@
         <v>36</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>36</v>
@@ -12712,10 +12711,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>36</v>
@@ -12724,22 +12723,22 @@
         <v>36</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>36</v>
@@ -12788,19 +12787,19 @@
         <v>36</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>36</v>
@@ -12809,10 +12808,10 @@
         <v>36</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>36</v>
@@ -12837,7 +12836,7 @@
         <v>34</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>36</v>
@@ -12846,19 +12845,19 @@
         <v>36</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12908,19 +12907,19 @@
         <v>36</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>36</v>
@@ -12929,10 +12928,10 @@
         <v>36</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>36</v>
@@ -12954,10 +12953,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>36</v>
@@ -12966,22 +12965,22 @@
         <v>36</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>36</v>
@@ -13030,19 +13029,19 @@
         <v>36</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>36</v>
@@ -13051,10 +13050,10 @@
         <v>36</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>36</v>
@@ -13079,7 +13078,7 @@
         <v>34</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>36</v>
@@ -13088,22 +13087,22 @@
         <v>36</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>36</v>
@@ -13152,19 +13151,19 @@
         <v>36</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>36</v>
@@ -13173,10 +13172,10 @@
         <v>36</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>36</v>
@@ -13201,7 +13200,7 @@
         <v>34</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>36</v>
@@ -13210,22 +13209,22 @@
         <v>36</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>36</v>
@@ -13274,19 +13273,19 @@
         <v>36</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>36</v>
@@ -13295,10 +13294,10 @@
         <v>36</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>36</v>
@@ -13323,7 +13322,7 @@
         <v>34</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>36</v>
@@ -13332,22 +13331,22 @@
         <v>36</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>36</v>
@@ -13396,19 +13395,19 @@
         <v>36</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>36</v>
@@ -13417,10 +13416,10 @@
         <v>36</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>36</v>
@@ -13445,7 +13444,7 @@
         <v>34</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>36</v>
@@ -13457,7 +13456,7 @@
         <v>36</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>520</v>
@@ -13494,7 +13493,7 @@
         <v>36</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y92" t="s" s="2">
         <v>524</v>
@@ -13524,13 +13523,13 @@
         <v>34</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>36</v>
@@ -13567,7 +13566,7 @@
         <v>34</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>36</v>
@@ -13579,13 +13578,13 @@
         <v>36</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13636,13 +13635,13 @@
         <v>36</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>36</v>
@@ -13660,7 +13659,7 @@
         <v>36</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>36</v>
@@ -13678,7 +13677,7 @@
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13697,16 +13696,16 @@
         <v>36</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13744,19 +13743,19 @@
         <v>36</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>34</v>
@@ -13765,10 +13764,10 @@
         <v>35</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>36</v>
@@ -13780,7 +13779,7 @@
         <v>36</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>36</v>
@@ -13814,22 +13813,22 @@
         <v>36</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>36</v>
@@ -13878,7 +13877,7 @@
         <v>36</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>34</v>
@@ -13887,10 +13886,10 @@
         <v>35</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>36</v>
@@ -13899,10 +13898,10 @@
         <v>36</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>36</v>
@@ -13927,7 +13926,7 @@
         <v>34</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>36</v>
@@ -13939,13 +13938,13 @@
         <v>36</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13996,13 +13995,13 @@
         <v>36</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>36</v>
@@ -14020,7 +14019,7 @@
         <v>36</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>36</v>
@@ -14038,7 +14037,7 @@
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14057,16 +14056,16 @@
         <v>36</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14104,19 +14103,19 @@
         <v>36</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>34</v>
@@ -14125,10 +14124,10 @@
         <v>35</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>36</v>
@@ -14140,7 +14139,7 @@
         <v>36</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>36</v>
@@ -14162,10 +14161,10 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>36</v>
@@ -14174,22 +14173,22 @@
         <v>36</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>36</v>
@@ -14238,19 +14237,19 @@
         <v>36</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>36</v>
@@ -14259,10 +14258,10 @@
         <v>36</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>36</v>
@@ -14287,7 +14286,7 @@
         <v>34</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>36</v>
@@ -14296,19 +14295,19 @@
         <v>36</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14358,19 +14357,19 @@
         <v>36</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>36</v>
@@ -14379,10 +14378,10 @@
         <v>36</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>36</v>
@@ -14404,10 +14403,10 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>36</v>
@@ -14416,22 +14415,22 @@
         <v>36</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>36</v>
@@ -14480,19 +14479,19 @@
         <v>36</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>36</v>
@@ -14501,10 +14500,10 @@
         <v>36</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>36</v>
@@ -14529,7 +14528,7 @@
         <v>34</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>36</v>
@@ -14538,22 +14537,22 @@
         <v>36</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>36</v>
@@ -14602,19 +14601,19 @@
         <v>36</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>36</v>
@@ -14623,10 +14622,10 @@
         <v>36</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>36</v>
@@ -14651,7 +14650,7 @@
         <v>34</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>36</v>
@@ -14660,22 +14659,22 @@
         <v>36</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>36</v>
@@ -14724,19 +14723,19 @@
         <v>36</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>36</v>
@@ -14745,10 +14744,10 @@
         <v>36</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>36</v>
@@ -14773,7 +14772,7 @@
         <v>34</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>36</v>
@@ -14782,22 +14781,22 @@
         <v>36</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>36</v>
@@ -14846,19 +14845,19 @@
         <v>36</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>36</v>
@@ -14867,10 +14866,10 @@
         <v>36</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>36</v>
@@ -14895,7 +14894,7 @@
         <v>34</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>36</v>
@@ -14972,13 +14971,13 @@
         <v>34</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>36</v>
@@ -15015,7 +15014,7 @@
         <v>34</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>36</v>
@@ -15092,13 +15091,13 @@
         <v>34</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>36</v>
@@ -15217,7 +15216,7 @@
         <v>35</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>562</v>
@@ -15257,7 +15256,7 @@
         <v>34</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>36</v>
@@ -15269,13 +15268,13 @@
         <v>36</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15326,13 +15325,13 @@
         <v>36</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>36</v>
@@ -15350,7 +15349,7 @@
         <v>36</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>36</v>
@@ -15368,7 +15367,7 @@
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15387,16 +15386,16 @@
         <v>36</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15434,19 +15433,19 @@
         <v>36</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>34</v>
@@ -15455,10 +15454,10 @@
         <v>35</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>36</v>
@@ -15470,7 +15469,7 @@
         <v>36</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>36</v>
@@ -15501,13 +15500,13 @@
         <v>36</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>569</v>
@@ -15516,10 +15515,10 @@
         <v>570</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>36</v>
@@ -15577,10 +15576,10 @@
         <v>35</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>36</v>
@@ -15592,7 +15591,7 @@
         <v>36</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>36</v>
@@ -15617,7 +15616,7 @@
         <v>34</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>36</v>
@@ -15694,7 +15693,7 @@
         <v>34</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>577</v>
@@ -15737,7 +15736,7 @@
         <v>34</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>36</v>
@@ -15814,7 +15813,7 @@
         <v>34</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>577</v>
@@ -15857,7 +15856,7 @@
         <v>34</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>36</v>
@@ -15869,7 +15868,7 @@
         <v>36</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>586</v>
@@ -15906,7 +15905,7 @@
         <v>36</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y112" t="s" s="2">
         <v>590</v>
@@ -15936,13 +15935,13 @@
         <v>34</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>36</v>
@@ -15991,7 +15990,7 @@
         <v>36</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>595</v>
@@ -16028,7 +16027,7 @@
         <v>36</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y113" t="s" s="2">
         <v>599</v>
@@ -16061,10 +16060,10 @@
         <v>35</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>36</v>
@@ -16101,7 +16100,7 @@
         <v>34</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>36</v>
@@ -16180,10 +16179,10 @@
         <v>34</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>607</v>
@@ -16223,7 +16222,7 @@
         <v>34</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>36</v>
@@ -16235,7 +16234,7 @@
         <v>36</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L115" t="s" s="2">
         <v>611</v>
@@ -16244,7 +16243,7 @@
         <v>612</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16300,13 +16299,13 @@
         <v>34</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>36</v>
@@ -16352,7 +16351,7 @@
         <v>36</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>615</v>
@@ -16423,10 +16422,10 @@
         <v>35</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>36</v>
@@ -16472,7 +16471,7 @@
         <v>36</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K117" t="s" s="2">
         <v>622</v>
@@ -16543,10 +16542,10 @@
         <v>35</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>36</v>
@@ -16586,13 +16585,13 @@
         <v>35</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K118" t="s" s="2">
         <v>557</v>
@@ -16665,7 +16664,7 @@
         <v>35</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>631</v>
@@ -16705,7 +16704,7 @@
         <v>34</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>36</v>
@@ -16717,13 +16716,13 @@
         <v>36</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16774,13 +16773,13 @@
         <v>36</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>36</v>
@@ -16798,7 +16797,7 @@
         <v>36</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>36</v>
@@ -16816,7 +16815,7 @@
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16835,16 +16834,16 @@
         <v>36</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16882,19 +16881,19 @@
         <v>36</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>34</v>
@@ -16903,10 +16902,10 @@
         <v>35</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>36</v>
@@ -16918,7 +16917,7 @@
         <v>36</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>36</v>
@@ -16949,13 +16948,13 @@
         <v>36</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L121" t="s" s="2">
         <v>569</v>
@@ -16964,10 +16963,10 @@
         <v>570</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>36</v>
@@ -17025,10 +17024,10 @@
         <v>35</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>36</v>
@@ -17040,7 +17039,7 @@
         <v>36</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>36</v>
@@ -17062,22 +17061,22 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L122" t="s" s="2">
         <v>638</v>
@@ -17114,13 +17113,13 @@
         <v>36</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>36</v>
@@ -17141,16 +17140,16 @@
         <v>637</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>36</v>
@@ -17159,13 +17158,13 @@
         <v>642</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>36</v>
@@ -17187,16 +17186,16 @@
         <v>34</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K123" t="s" s="2">
         <v>644</v>
@@ -17211,7 +17210,7 @@
         <v>647</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>36</v>
@@ -17236,7 +17235,7 @@
         <v>36</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y123" t="s" s="2">
         <v>648</v>
@@ -17266,13 +17265,13 @@
         <v>34</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>650</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>36</v>
@@ -17281,16 +17280,16 @@
         <v>651</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="124" hidden="true">
@@ -17309,10 +17308,10 @@
         <v>34</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>36</v>
@@ -17321,7 +17320,7 @@
         <v>36</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L124" t="s" s="2">
         <v>653</v>
@@ -17333,7 +17332,7 @@
         <v>655</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>36</v>
@@ -17358,13 +17357,13 @@
         <v>36</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>36</v>
@@ -17388,13 +17387,13 @@
         <v>34</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>656</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>36</v>
@@ -17403,10 +17402,10 @@
         <v>36</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>36</v>
@@ -17424,7 +17423,7 @@
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -17443,19 +17442,19 @@
         <v>36</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>36</v>
@@ -17480,13 +17479,13 @@
         <v>36</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>485</v>
+        <v>658</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>658</v>
+        <v>486</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>36</v>
@@ -17513,10 +17512,10 @@
         <v>35</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>36</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:09:26+00:00</t>
+    <t>2023-09-19T16:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:18:04+00:00</t>
+    <t>2023-09-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T15:08:45+00:00</t>
+    <t>2023-09-27T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:45:14+00:00</t>
+    <t>2023-11-23T10:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4914" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4914" uniqueCount="707">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-23T10:14:09+00:00</t>
+    <t>2023-11-28T12:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,11 +440,10 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.</t>
-  </si>
-  <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.
-L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -645,6 +644,9 @@
     <t>Permet de définir le niveau d'effort (au repos, à l'effort, après l'effort) lors de la mesure de la fréquence respiratoire</t>
   </si>
   <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
     <t>Observation.extension:supportingInfo</t>
   </si>
   <si>
@@ -675,7 +677,7 @@
   </si>
   <si>
     <t>Motif de la mesure
-Texte libre (ex. infection, insolation, vaccination…)</t>
+Texte libre (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…)</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -4661,7 +4663,7 @@
         <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4747,13 +4749,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>113</v>
@@ -4775,13 +4777,13 @@
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>117</v>
@@ -4869,13 +4871,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>80</v>
@@ -4897,13 +4899,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4989,10 +4991,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5018,16 +5020,16 @@
         <v>114</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -5076,7 +5078,7 @@
         <v>120</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -5111,10 +5113,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5137,17 +5139,17 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5196,7 +5198,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5211,19 +5213,19 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -5231,14 +5233,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5257,19 +5259,19 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -5318,7 +5320,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5330,19 +5332,19 @@
         <v>103</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -5353,14 +5355,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5379,16 +5381,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5438,7 +5440,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5450,19 +5452,19 @@
         <v>103</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
@@ -5473,10 +5475,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5502,16 +5504,16 @@
         <v>171</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5536,13 +5538,13 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
@@ -5560,7 +5562,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -5575,19 +5577,19 @@
         <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5595,10 +5597,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5621,19 +5623,19 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5661,16 +5663,16 @@
         <v>175</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -5680,7 +5682,7 @@
         <v>120</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5701,13 +5703,13 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>80</v>
@@ -5715,13 +5717,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>80</v>
@@ -5743,19 +5745,19 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -5783,10 +5785,10 @@
         <v>175</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5804,7 +5806,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5825,13 +5827,13 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>80</v>
@@ -5839,10 +5841,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5957,10 +5959,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6077,10 +6079,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6106,16 +6108,16 @@
         <v>147</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -6164,7 +6166,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -6185,10 +6187,10 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>80</v>
@@ -6199,10 +6201,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6317,10 +6319,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6437,10 +6439,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6466,23 +6468,23 @@
         <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>80</v>
@@ -6524,7 +6526,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6545,10 +6547,10 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6559,10 +6561,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6588,13 +6590,13 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6644,7 +6646,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6665,10 +6667,10 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6679,10 +6681,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6708,23 +6710,23 @@
         <v>171</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>80</v>
@@ -6766,7 +6768,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6787,10 +6789,10 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6801,10 +6803,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6830,16 +6832,16 @@
         <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6888,7 +6890,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6909,10 +6911,10 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6923,10 +6925,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6949,19 +6951,19 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -7010,7 +7012,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -7031,10 +7033,10 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -7045,10 +7047,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7074,16 +7076,16 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -7132,7 +7134,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -7153,10 +7155,10 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -7167,14 +7169,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7193,19 +7195,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -7233,10 +7235,10 @@
         <v>151</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -7254,7 +7256,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -7269,30 +7271,30 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7407,10 +7409,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7527,10 +7529,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7556,16 +7558,16 @@
         <v>147</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7602,7 +7604,7 @@
         <v>80</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7612,7 +7614,7 @@
         <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7633,10 +7635,10 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7647,13 +7649,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>80</v>
@@ -7678,16 +7680,16 @@
         <v>147</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7736,7 +7738,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7757,10 +7759,10 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7771,10 +7773,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7889,10 +7891,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8009,10 +8011,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8038,23 +8040,23 @@
         <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>80</v>
@@ -8096,7 +8098,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -8117,10 +8119,10 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -8131,10 +8133,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8160,13 +8162,13 @@
         <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8216,7 +8218,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -8237,10 +8239,10 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -8251,10 +8253,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8280,23 +8282,23 @@
         <v>171</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>80</v>
@@ -8338,7 +8340,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8359,10 +8361,10 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -8373,10 +8375,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8402,16 +8404,16 @@
         <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8460,7 +8462,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8481,10 +8483,10 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -8495,10 +8497,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8521,19 +8523,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8582,7 +8584,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8603,10 +8605,10 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8617,10 +8619,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8646,16 +8648,16 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8704,7 +8706,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8725,10 +8727,10 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8739,10 +8741,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8765,19 +8767,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8826,7 +8828,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8838,22 +8840,22 @@
         <v>103</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8861,10 +8863,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8887,16 +8889,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8946,7 +8948,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8958,7 +8960,7 @@
         <v>103</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
@@ -8967,13 +8969,13 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8981,14 +8983,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9007,19 +9009,19 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -9068,7 +9070,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -9080,22 +9082,22 @@
         <v>103</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -9103,14 +9105,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9129,19 +9131,19 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -9190,7 +9192,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -9199,25 +9201,25 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9225,10 +9227,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9254,13 +9256,13 @@
         <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9310,7 +9312,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9331,13 +9333,13 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -9345,10 +9347,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9371,19 +9373,19 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -9432,7 +9434,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9444,22 +9446,22 @@
         <v>103</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -9467,10 +9469,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9493,19 +9495,19 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -9542,17 +9544,17 @@
         <v>80</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9561,7 +9563,7 @@
         <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>104</v>
@@ -9570,30 +9572,30 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>80</v>
@@ -9615,19 +9617,19 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9637,7 +9639,7 @@
         <v>80</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>80</v>
@@ -9676,7 +9678,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9685,7 +9687,7 @@
         <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
@@ -9694,27 +9696,27 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9829,10 +9831,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9949,10 +9951,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9975,19 +9977,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -10036,7 +10038,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -10057,10 +10059,10 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -10071,10 +10073,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10100,22 +10102,22 @@
         <v>171</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>80</v>
@@ -10136,13 +10138,13 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -10160,7 +10162,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -10181,10 +10183,10 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -10195,10 +10197,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10224,16 +10226,16 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -10282,7 +10284,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10303,10 +10305,10 @@
         <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -10317,10 +10319,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10346,23 +10348,23 @@
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>80</v>
@@ -10404,7 +10406,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10413,7 +10415,7 @@
         <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>104</v>
@@ -10425,10 +10427,10 @@
         <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
@@ -10439,10 +10441,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10468,16 +10470,16 @@
         <v>171</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -10502,13 +10504,13 @@
         <v>80</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>80</v>
@@ -10526,7 +10528,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10547,10 +10549,10 @@
         <v>80</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -10561,10 +10563,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10587,19 +10589,19 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10627,10 +10629,10 @@
         <v>151</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10648,7 +10650,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10657,7 +10659,7 @@
         <v>91</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10672,7 +10674,7 @@
         <v>105</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
@@ -10683,10 +10685,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10801,10 +10803,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10921,10 +10923,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10950,16 +10952,16 @@
         <v>147</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -11008,7 +11010,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -11029,10 +11031,10 @@
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -11043,10 +11045,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11161,10 +11163,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11281,10 +11283,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11310,16 +11312,16 @@
         <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -11368,7 +11370,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11389,10 +11391,10 @@
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -11403,10 +11405,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11432,13 +11434,13 @@
         <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11488,7 +11490,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11509,10 +11511,10 @@
         <v>80</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -11523,10 +11525,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11552,16 +11554,16 @@
         <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11610,7 +11612,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11631,10 +11633,10 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11645,10 +11647,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11674,16 +11676,16 @@
         <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11732,7 +11734,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11753,10 +11755,10 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11767,10 +11769,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11793,19 +11795,19 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11854,7 +11856,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11875,10 +11877,10 @@
         <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -11889,10 +11891,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11918,16 +11920,16 @@
         <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11976,7 +11978,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11997,10 +11999,10 @@
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -12011,14 +12013,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12037,19 +12039,19 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -12078,7 +12080,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -12096,7 +12098,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -12114,27 +12116,27 @@
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12157,19 +12159,19 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -12218,7 +12220,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12239,10 +12241,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12253,10 +12255,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12279,16 +12281,16 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12314,11 +12316,11 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -12336,7 +12338,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12354,27 +12356,27 @@
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12489,10 +12491,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12609,10 +12611,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12638,16 +12640,16 @@
         <v>147</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -12696,7 +12698,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12717,10 +12719,10 @@
         <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12731,10 +12733,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12849,10 +12851,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12969,10 +12971,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12998,16 +13000,16 @@
         <v>135</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -13056,7 +13058,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -13077,10 +13079,10 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -13091,10 +13093,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13120,13 +13122,13 @@
         <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13176,7 +13178,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13197,10 +13199,10 @@
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13211,10 +13213,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13240,16 +13242,16 @@
         <v>171</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -13298,7 +13300,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13319,10 +13321,10 @@
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -13333,10 +13335,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13362,16 +13364,16 @@
         <v>107</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13420,7 +13422,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13441,10 +13443,10 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13455,10 +13457,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13481,19 +13483,19 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13542,7 +13544,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13563,10 +13565,10 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -13577,10 +13579,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13606,16 +13608,16 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13664,7 +13666,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13685,10 +13687,10 @@
         <v>80</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13699,10 +13701,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13725,19 +13727,19 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13762,13 +13764,13 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13786,7 +13788,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13807,10 +13809,10 @@
         <v>80</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13821,10 +13823,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13939,10 +13941,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14059,10 +14061,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14088,16 +14090,16 @@
         <v>147</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -14146,7 +14148,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14167,10 +14169,10 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14181,10 +14183,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14299,10 +14301,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14419,10 +14421,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14448,16 +14450,16 @@
         <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>80</v>
@@ -14506,7 +14508,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14527,10 +14529,10 @@
         <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14541,10 +14543,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14570,13 +14572,13 @@
         <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14626,7 +14628,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14647,10 +14649,10 @@
         <v>80</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14661,10 +14663,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14690,16 +14692,16 @@
         <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14748,7 +14750,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14769,10 +14771,10 @@
         <v>80</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>80</v>
@@ -14783,10 +14785,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14812,16 +14814,16 @@
         <v>107</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>80</v>
@@ -14870,7 +14872,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14891,10 +14893,10 @@
         <v>80</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>80</v>
@@ -14905,10 +14907,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14931,19 +14933,19 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -14992,7 +14994,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -15013,10 +15015,10 @@
         <v>80</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>80</v>
@@ -15027,10 +15029,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15056,16 +15058,16 @@
         <v>107</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -15114,7 +15116,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -15135,10 +15137,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -15149,10 +15151,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15175,16 +15177,16 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15234,7 +15236,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15246,33 +15248,33 @@
         <v>103</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15295,16 +15297,16 @@
         <v>80</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15354,7 +15356,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15366,33 +15368,33 @@
         <v>103</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15415,19 +15417,19 @@
         <v>80</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>80</v>
@@ -15476,7 +15478,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15488,7 +15490,7 @@
         <v>103</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>80</v>
@@ -15497,10 +15499,10 @@
         <v>80</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15511,10 +15513,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15629,10 +15631,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15749,14 +15751,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15778,16 +15780,16 @@
         <v>114</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>80</v>
@@ -15836,7 +15838,7 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15871,10 +15873,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15897,16 +15899,16 @@
         <v>80</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15956,7 +15958,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15965,10 +15967,10 @@
         <v>91</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>80</v>
@@ -15977,10 +15979,10 @@
         <v>80</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -15991,10 +15993,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16017,16 +16019,16 @@
         <v>80</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16076,7 +16078,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -16085,10 +16087,10 @@
         <v>91</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>80</v>
@@ -16097,10 +16099,10 @@
         <v>80</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>80</v>
@@ -16111,10 +16113,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16137,19 +16139,19 @@
         <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -16177,10 +16179,10 @@
         <v>175</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>80</v>
@@ -16198,7 +16200,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -16216,13 +16218,13 @@
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -16233,10 +16235,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16259,19 +16261,19 @@
         <v>80</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>80</v>
@@ -16299,10 +16301,10 @@
         <v>161</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>80</v>
@@ -16320,7 +16322,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16338,13 +16340,13 @@
         <v>80</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16355,10 +16357,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16381,19 +16383,19 @@
         <v>80</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>80</v>
@@ -16442,7 +16444,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16454,7 +16456,7 @@
         <v>103</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>80</v>
@@ -16463,10 +16465,10 @@
         <v>80</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
@@ -16477,10 +16479,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16506,13 +16508,13 @@
         <v>107</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16562,7 +16564,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16583,10 +16585,10 @@
         <v>80</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>80</v>
@@ -16597,10 +16599,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16623,16 +16625,16 @@
         <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16682,7 +16684,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16694,7 +16696,7 @@
         <v>103</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>80</v>
@@ -16703,10 +16705,10 @@
         <v>80</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>80</v>
@@ -16717,10 +16719,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16743,16 +16745,16 @@
         <v>92</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16802,7 +16804,7 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16814,7 +16816,7 @@
         <v>103</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>80</v>
@@ -16823,10 +16825,10 @@
         <v>80</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>80</v>
@@ -16837,10 +16839,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16863,19 +16865,19 @@
         <v>92</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>80</v>
@@ -16924,7 +16926,7 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16936,7 +16938,7 @@
         <v>103</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>80</v>
@@ -16945,10 +16947,10 @@
         <v>80</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>80</v>
@@ -16959,10 +16961,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17077,10 +17079,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17197,14 +17199,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -17226,16 +17228,16 @@
         <v>114</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>80</v>
@@ -17284,7 +17286,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17319,10 +17321,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17345,19 +17347,19 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17385,10 +17387,10 @@
         <v>151</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>80</v>
@@ -17406,7 +17408,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>91</v>
@@ -17424,16 +17426,16 @@
         <v>80</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>80</v>
@@ -17441,10 +17443,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17467,19 +17469,19 @@
         <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>80</v>
@@ -17504,13 +17506,13 @@
         <v>80</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>80</v>
@@ -17528,7 +17530,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17537,7 +17539,7 @@
         <v>91</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>104</v>
@@ -17546,27 +17548,27 @@
         <v>80</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17589,19 +17591,19 @@
         <v>80</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -17629,10 +17631,10 @@
         <v>151</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>80</v>
@@ -17650,7 +17652,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17659,7 +17661,7 @@
         <v>91</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>104</v>
@@ -17674,7 +17676,7 @@
         <v>105</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>80</v>
@@ -17685,14 +17687,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17711,19 +17713,19 @@
         <v>80</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>80</v>
@@ -17751,28 +17753,28 @@
         <v>151</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17790,27 +17792,27 @@
         <v>80</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17836,16 +17838,16 @@
         <v>81</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>80</v>
@@ -17894,7 +17896,7 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17915,10 +17917,10 @@
         <v>80</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$116</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4914" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4491" uniqueCount="696">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:14:54+00:00</t>
+    <t>2023-11-28T12:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1792,39 +1792,6 @@
   </si>
   <si>
     <t>methodCode</t>
-  </si>
-  <si>
-    <t>Observation.method.id</t>
-  </si>
-  <si>
-    <t>Observation.method.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.method.text</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -2537,7 +2504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP127"/>
+  <dimension ref="A1:AP116"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.58984375" customWidth="true" bestFit="true"/>
@@ -2564,7 +2531,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="109.11328125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="111.65625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -13718,7 +13685,7 @@
         <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>80</v>
@@ -13764,11 +13731,9 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>569</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
         <v>569</v>
       </c>
@@ -13849,15 +13814,17 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>107</v>
+        <v>573</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>108</v>
+        <v>574</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13906,7 +13873,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>110</v>
+        <v>572</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13915,47 +13882,47 @@
         <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>80</v>
+        <v>577</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>80</v>
+        <v>578</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>111</v>
+        <v>579</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>80</v>
+        <v>580</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>80</v>
@@ -13967,16 +13934,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>114</v>
+        <v>582</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>115</v>
+        <v>583</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>116</v>
+        <v>584</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>117</v>
+        <v>585</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14014,57 +13981,57 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>121</v>
+        <v>581</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>122</v>
+        <v>233</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>80</v>
+        <v>586</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>80</v>
+        <v>587</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>105</v>
+        <v>588</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>80</v>
+        <v>589</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14084,22 +14051,22 @@
         <v>80</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>147</v>
+        <v>591</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>279</v>
+        <v>592</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>280</v>
+        <v>593</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>281</v>
+        <v>594</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>282</v>
+        <v>595</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -14148,7 +14115,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>283</v>
+        <v>590</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14160,7 +14127,7 @@
         <v>103</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>104</v>
+        <v>596</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>80</v>
@@ -14169,10 +14136,10 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>284</v>
+        <v>597</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>285</v>
+        <v>598</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14183,10 +14150,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14301,10 +14268,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14421,45 +14388,45 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>80</v>
+        <v>602</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>292</v>
+        <v>603</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>293</v>
+        <v>604</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>294</v>
+        <v>117</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>295</v>
+        <v>215</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>80</v>
@@ -14508,19 +14475,19 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>297</v>
+        <v>605</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>80</v>
@@ -14529,10 +14496,10 @@
         <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>298</v>
+        <v>80</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14543,10 +14510,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14566,19 +14533,19 @@
         <v>80</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>107</v>
+        <v>607</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>302</v>
+        <v>608</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>303</v>
+        <v>609</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>304</v>
+        <v>610</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14628,7 +14595,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>305</v>
+        <v>606</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14637,10 +14604,10 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>103</v>
+        <v>611</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>104</v>
+        <v>612</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>80</v>
@@ -14649,10 +14616,10 @@
         <v>80</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>306</v>
+        <v>613</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>307</v>
+        <v>614</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14663,10 +14630,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>579</v>
+        <v>615</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>579</v>
+        <v>615</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14674,7 +14641,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>91</v>
@@ -14686,23 +14653,21 @@
         <v>80</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>171</v>
+        <v>607</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>310</v>
+        <v>616</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>311</v>
+        <v>617</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>80</v>
       </c>
@@ -14750,7 +14715,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>315</v>
+        <v>615</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14759,10 +14724,10 @@
         <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>103</v>
+        <v>611</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>104</v>
+        <v>612</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>80</v>
@@ -14771,10 +14736,10 @@
         <v>80</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>316</v>
+        <v>613</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>317</v>
+        <v>618</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>80</v>
@@ -14785,10 +14750,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>580</v>
+        <v>619</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>580</v>
+        <v>619</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14808,22 +14773,22 @@
         <v>80</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>107</v>
+        <v>260</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>320</v>
+        <v>620</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>321</v>
+        <v>621</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>312</v>
+        <v>622</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>322</v>
+        <v>623</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>80</v>
@@ -14848,13 +14813,13 @@
         <v>80</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>80</v>
+        <v>624</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>80</v>
+        <v>625</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>80</v>
@@ -14872,7 +14837,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>323</v>
+        <v>619</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14890,13 +14855,13 @@
         <v>80</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>80</v>
+        <v>626</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>324</v>
+        <v>627</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>325</v>
+        <v>534</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>80</v>
@@ -14907,10 +14872,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14921,7 +14886,7 @@
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>80</v>
@@ -14930,22 +14895,22 @@
         <v>80</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>328</v>
+        <v>260</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>329</v>
+        <v>629</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>330</v>
+        <v>630</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>331</v>
+        <v>631</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>332</v>
+        <v>632</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -14970,13 +14935,13 @@
         <v>80</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>80</v>
+        <v>633</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>80</v>
+        <v>634</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>80</v>
@@ -14994,13 +14959,13 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>333</v>
+        <v>628</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>103</v>
@@ -15012,13 +14977,13 @@
         <v>80</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>80</v>
+        <v>626</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>334</v>
+        <v>627</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>335</v>
+        <v>534</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>80</v>
@@ -15029,10 +14994,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>582</v>
+        <v>635</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>582</v>
+        <v>635</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15052,22 +15017,22 @@
         <v>80</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>107</v>
+        <v>636</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>338</v>
+        <v>637</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>339</v>
+        <v>638</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>340</v>
+        <v>639</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>341</v>
+        <v>640</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -15116,7 +15081,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>342</v>
+        <v>635</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -15128,7 +15093,7 @@
         <v>103</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>104</v>
+        <v>641</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>80</v>
@@ -15137,10 +15102,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>343</v>
+        <v>642</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>344</v>
+        <v>643</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -15151,10 +15116,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>583</v>
+        <v>644</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>583</v>
+        <v>644</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15177,16 +15142,16 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>584</v>
+        <v>107</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>585</v>
+        <v>645</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>586</v>
+        <v>646</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>587</v>
+        <v>312</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15236,7 +15201,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>583</v>
+        <v>644</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15248,33 +15213,33 @@
         <v>103</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>233</v>
+        <v>104</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>590</v>
+        <v>647</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>591</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>592</v>
+        <v>648</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>592</v>
+        <v>648</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15285,7 +15250,7 @@
         <v>78</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>80</v>
@@ -15294,19 +15259,19 @@
         <v>80</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>593</v>
+        <v>649</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>594</v>
+        <v>650</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>595</v>
+        <v>651</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>596</v>
+        <v>652</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15356,13 +15321,13 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>592</v>
+        <v>648</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>103</v>
@@ -15374,27 +15339,27 @@
         <v>80</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>597</v>
+        <v>80</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>598</v>
+        <v>653</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>599</v>
+        <v>654</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>600</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>601</v>
+        <v>655</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>601</v>
+        <v>655</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15414,23 +15379,21 @@
         <v>80</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>602</v>
+        <v>656</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>603</v>
+        <v>657</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>604</v>
+        <v>658</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>606</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>80</v>
       </c>
@@ -15478,7 +15441,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>601</v>
+        <v>655</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15490,7 +15453,7 @@
         <v>103</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>607</v>
+        <v>233</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>80</v>
@@ -15499,10 +15462,10 @@
         <v>80</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>608</v>
+        <v>653</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>609</v>
+        <v>660</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15513,10 +15476,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>610</v>
+        <v>661</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>610</v>
+        <v>661</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15527,28 +15490,32 @@
         <v>78</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>107</v>
+        <v>591</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>108</v>
+        <v>662</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>664</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>80</v>
       </c>
@@ -15596,19 +15563,19 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>110</v>
+        <v>661</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>80</v>
+        <v>665</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>80</v>
@@ -15617,10 +15584,10 @@
         <v>80</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>80</v>
+        <v>666</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>111</v>
+        <v>667</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>80</v>
@@ -15631,21 +15598,21 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>611</v>
+        <v>668</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>611</v>
+        <v>668</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>80</v>
@@ -15657,17 +15624,15 @@
         <v>80</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>80</v>
@@ -15704,31 +15669,31 @@
         <v>80</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>80</v>
@@ -15740,7 +15705,7 @@
         <v>80</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>80</v>
@@ -15751,14 +15716,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>612</v>
+        <v>669</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>612</v>
+        <v>669</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>613</v>
+        <v>113</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15771,26 +15736,24 @@
         <v>80</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K110" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>614</v>
+        <v>115</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>615</v>
+        <v>116</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O110" t="s" s="2">
-        <v>215</v>
-      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>80</v>
       </c>
@@ -15826,19 +15789,19 @@
         <v>80</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>616</v>
+        <v>121</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15873,44 +15836,46 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>617</v>
+        <v>670</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>617</v>
+        <v>670</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>80</v>
+        <v>602</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>618</v>
+        <v>114</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O111" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>80</v>
       </c>
@@ -15958,19 +15923,19 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>622</v>
+        <v>103</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>623</v>
+        <v>122</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>80</v>
@@ -15979,10 +15944,10 @@
         <v>80</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>624</v>
+        <v>80</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>625</v>
+        <v>105</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -15993,10 +15958,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>626</v>
+        <v>671</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>626</v>
+        <v>671</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16004,33 +15969,35 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>618</v>
+        <v>260</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>627</v>
+        <v>672</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>628</v>
+        <v>673</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O112" s="2"/>
+        <v>674</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>675</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>80</v>
       </c>
@@ -16054,13 +16021,13 @@
         <v>80</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>80</v>
@@ -16078,34 +16045,34 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>626</v>
+        <v>671</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>622</v>
+        <v>103</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>623</v>
+        <v>104</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>80</v>
+        <v>676</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>624</v>
+        <v>355</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>629</v>
+        <v>356</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>80</v>
@@ -16113,10 +16080,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16130,28 +16097,28 @@
         <v>91</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>260</v>
+        <v>678</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>631</v>
+        <v>679</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>632</v>
+        <v>680</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>633</v>
+        <v>681</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>634</v>
+        <v>442</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -16176,13 +16143,13 @@
         <v>80</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>175</v>
+        <v>251</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>636</v>
+        <v>683</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>80</v>
@@ -16200,7 +16167,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -16209,7 +16176,7 @@
         <v>91</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>103</v>
+        <v>684</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>104</v>
@@ -16218,27 +16185,27 @@
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>637</v>
+        <v>685</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>638</v>
+        <v>447</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>534</v>
+        <v>448</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16249,10 +16216,10 @@
         <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>80</v>
@@ -16264,16 +16231,16 @@
         <v>260</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>640</v>
+        <v>687</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>641</v>
+        <v>688</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>642</v>
+        <v>689</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>643</v>
+        <v>509</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>80</v>
@@ -16298,13 +16265,13 @@
         <v>80</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>644</v>
+        <v>510</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>645</v>
+        <v>511</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>80</v>
@@ -16322,16 +16289,16 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>103</v>
+        <v>690</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>104</v>
@@ -16340,13 +16307,13 @@
         <v>80</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>637</v>
+        <v>80</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>638</v>
+        <v>105</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16357,21 +16324,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>646</v>
+        <v>691</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>646</v>
+        <v>691</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>80</v>
+        <v>526</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>80</v>
@@ -16383,19 +16350,19 @@
         <v>80</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>647</v>
+        <v>260</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>648</v>
+        <v>527</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>649</v>
+        <v>528</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>650</v>
+        <v>529</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>651</v>
+        <v>530</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>80</v>
@@ -16420,13 +16387,13 @@
         <v>80</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>80</v>
+        <v>692</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>80</v>
+        <v>531</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>80</v>
@@ -16444,45 +16411,45 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>646</v>
+        <v>691</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>652</v>
+        <v>104</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>80</v>
+        <v>532</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>653</v>
+        <v>533</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>654</v>
+        <v>534</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>80</v>
+        <v>535</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>655</v>
+        <v>693</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>655</v>
+        <v>693</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16493,7 +16460,7 @@
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>80</v>
@@ -16505,18 +16472,20 @@
         <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>656</v>
+        <v>694</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>657</v>
+        <v>695</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>80</v>
       </c>
@@ -16564,19 +16533,19 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>655</v>
+        <v>693</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>80</v>
@@ -16585,1352 +16554,20 @@
         <v>80</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>624</v>
+        <v>597</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>658</v>
+        <v>598</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP119" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="P124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="P127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP127" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP127">
+  <autoFilter ref="A1:AP116">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17940,7 +16577,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI126">
+  <conditionalFormatting sqref="A2:AI115">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$127</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4491" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4914" uniqueCount="707">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:15:35+00:00</t>
+    <t>2023-11-28T12:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1792,6 +1792,39 @@
   </si>
   <si>
     <t>methodCode</t>
+  </si>
+  <si>
+    <t>Observation.method.id</t>
+  </si>
+  <si>
+    <t>Observation.method.extension</t>
+  </si>
+  <si>
+    <t>Observation.method.coding</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.method.text</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -2504,7 +2537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP116"/>
+  <dimension ref="A1:AP127"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.58984375" customWidth="true" bestFit="true"/>
@@ -2531,7 +2564,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="109.11328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="111.65625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -13685,7 +13718,7 @@
         <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>80</v>
@@ -13731,9 +13764,11 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y93" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="Z93" t="s" s="2">
         <v>569</v>
       </c>
@@ -13814,17 +13849,15 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>573</v>
+        <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>574</v>
+        <v>108</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13873,7 +13906,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>572</v>
+        <v>110</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13882,47 +13915,47 @@
         <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>577</v>
+        <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>578</v>
+        <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>579</v>
+        <v>111</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>580</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>80</v>
@@ -13934,16 +13967,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>582</v>
+        <v>114</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>583</v>
+        <v>115</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>584</v>
+        <v>116</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>585</v>
+        <v>117</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13981,57 +14014,57 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>581</v>
+        <v>121</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>586</v>
+        <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>587</v>
+        <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>588</v>
+        <v>105</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>589</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14051,22 +14084,22 @@
         <v>80</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>591</v>
+        <v>147</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>592</v>
+        <v>279</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>593</v>
+        <v>280</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>594</v>
+        <v>281</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>595</v>
+        <v>282</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -14115,7 +14148,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>590</v>
+        <v>283</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14127,7 +14160,7 @@
         <v>103</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>596</v>
+        <v>104</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>80</v>
@@ -14136,10 +14169,10 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>597</v>
+        <v>284</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>598</v>
+        <v>285</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14150,10 +14183,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14268,10 +14301,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14388,45 +14421,45 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>601</v>
+        <v>577</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>601</v>
+        <v>577</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>602</v>
+        <v>80</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>603</v>
+        <v>292</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>604</v>
+        <v>293</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>117</v>
+        <v>294</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>215</v>
+        <v>295</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>80</v>
@@ -14475,19 +14508,19 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>605</v>
+        <v>297</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>80</v>
@@ -14496,10 +14529,10 @@
         <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14510,10 +14543,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>606</v>
+        <v>578</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>606</v>
+        <v>578</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14533,19 +14566,19 @@
         <v>80</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>607</v>
+        <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>608</v>
+        <v>302</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>609</v>
+        <v>303</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>610</v>
+        <v>304</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14595,7 +14628,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>606</v>
+        <v>305</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14604,10 +14637,10 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>611</v>
+        <v>103</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>612</v>
+        <v>104</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>80</v>
@@ -14616,10 +14649,10 @@
         <v>80</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>613</v>
+        <v>306</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>614</v>
+        <v>307</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14630,10 +14663,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>615</v>
+        <v>579</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>615</v>
+        <v>579</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14641,7 +14674,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>91</v>
@@ -14653,21 +14686,23 @@
         <v>80</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>607</v>
+        <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>616</v>
+        <v>310</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>617</v>
+        <v>311</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
       </c>
@@ -14715,7 +14750,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>615</v>
+        <v>315</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14724,10 +14759,10 @@
         <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>611</v>
+        <v>103</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>612</v>
+        <v>104</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>80</v>
@@ -14736,10 +14771,10 @@
         <v>80</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>613</v>
+        <v>316</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>618</v>
+        <v>317</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>80</v>
@@ -14750,10 +14785,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>619</v>
+        <v>580</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>619</v>
+        <v>580</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14773,22 +14808,22 @@
         <v>80</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>260</v>
+        <v>107</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>620</v>
+        <v>320</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>621</v>
+        <v>321</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>622</v>
+        <v>312</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>623</v>
+        <v>322</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>80</v>
@@ -14813,13 +14848,13 @@
         <v>80</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>624</v>
+        <v>80</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>625</v>
+        <v>80</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>80</v>
@@ -14837,7 +14872,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>619</v>
+        <v>323</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14855,13 +14890,13 @@
         <v>80</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>626</v>
+        <v>80</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>627</v>
+        <v>324</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>534</v>
+        <v>325</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>80</v>
@@ -14872,10 +14907,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>628</v>
+        <v>581</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>628</v>
+        <v>581</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14886,7 +14921,7 @@
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>80</v>
@@ -14895,22 +14930,22 @@
         <v>80</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>260</v>
+        <v>328</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>629</v>
+        <v>329</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>630</v>
+        <v>330</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>631</v>
+        <v>331</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>632</v>
+        <v>332</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -14935,13 +14970,13 @@
         <v>80</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>633</v>
+        <v>80</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>634</v>
+        <v>80</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>80</v>
@@ -14959,13 +14994,13 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>628</v>
+        <v>333</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>103</v>
@@ -14977,13 +15012,13 @@
         <v>80</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>626</v>
+        <v>80</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>627</v>
+        <v>334</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>534</v>
+        <v>335</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>80</v>
@@ -14994,10 +15029,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>635</v>
+        <v>582</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>635</v>
+        <v>582</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15017,22 +15052,22 @@
         <v>80</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>636</v>
+        <v>107</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>637</v>
+        <v>338</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>638</v>
+        <v>339</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>639</v>
+        <v>340</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>640</v>
+        <v>341</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -15081,7 +15116,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>635</v>
+        <v>342</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -15093,7 +15128,7 @@
         <v>103</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>641</v>
+        <v>104</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>80</v>
@@ -15102,10 +15137,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>642</v>
+        <v>343</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>643</v>
+        <v>344</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -15116,10 +15151,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>644</v>
+        <v>583</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>644</v>
+        <v>583</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15142,16 +15177,16 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>107</v>
+        <v>584</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>645</v>
+        <v>585</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>646</v>
+        <v>586</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>312</v>
+        <v>587</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15201,7 +15236,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>644</v>
+        <v>583</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15213,33 +15248,33 @@
         <v>103</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>104</v>
+        <v>233</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>80</v>
+        <v>588</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>613</v>
+        <v>589</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>647</v>
+        <v>590</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>80</v>
+        <v>591</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>648</v>
+        <v>592</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>648</v>
+        <v>592</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15250,7 +15285,7 @@
         <v>78</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>80</v>
@@ -15259,19 +15294,19 @@
         <v>80</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>649</v>
+        <v>593</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>650</v>
+        <v>594</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>651</v>
+        <v>595</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>652</v>
+        <v>596</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15321,13 +15356,13 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>648</v>
+        <v>592</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>103</v>
@@ -15339,27 +15374,27 @@
         <v>80</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>80</v>
+        <v>597</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>653</v>
+        <v>598</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>654</v>
+        <v>599</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>80</v>
+        <v>600</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>655</v>
+        <v>601</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>655</v>
+        <v>601</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15379,21 +15414,23 @@
         <v>80</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>656</v>
+        <v>602</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>657</v>
+        <v>603</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>658</v>
+        <v>604</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>80</v>
       </c>
@@ -15441,7 +15478,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>655</v>
+        <v>601</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15453,7 +15490,7 @@
         <v>103</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>233</v>
+        <v>607</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>80</v>
@@ -15462,10 +15499,10 @@
         <v>80</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>653</v>
+        <v>608</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>660</v>
+        <v>609</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15476,10 +15513,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>661</v>
+        <v>610</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>661</v>
+        <v>610</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15490,32 +15527,28 @@
         <v>78</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>591</v>
+        <v>107</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>662</v>
+        <v>108</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>664</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>80</v>
       </c>
@@ -15563,19 +15596,19 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>661</v>
+        <v>110</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>665</v>
+        <v>80</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>80</v>
@@ -15584,10 +15617,10 @@
         <v>80</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>666</v>
+        <v>80</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>667</v>
+        <v>111</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>80</v>
@@ -15598,21 +15631,21 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>668</v>
+        <v>611</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>668</v>
+        <v>611</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>80</v>
@@ -15624,15 +15657,17 @@
         <v>80</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>80</v>
@@ -15669,31 +15704,31 @@
         <v>80</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>80</v>
@@ -15705,7 +15740,7 @@
         <v>80</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>80</v>
@@ -15716,14 +15751,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>669</v>
+        <v>612</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>669</v>
+        <v>612</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>113</v>
+        <v>613</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15736,24 +15771,26 @@
         <v>80</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K110" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>115</v>
+        <v>614</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>116</v>
+        <v>615</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O110" s="2"/>
+      <c r="O110" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>80</v>
       </c>
@@ -15789,19 +15826,19 @@
         <v>80</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>121</v>
+        <v>616</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15836,46 +15873,44 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>670</v>
+        <v>617</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>670</v>
+        <v>617</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>602</v>
+        <v>80</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>114</v>
+        <v>618</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>80</v>
       </c>
@@ -15923,19 +15958,19 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>103</v>
+        <v>622</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>122</v>
+        <v>623</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>80</v>
@@ -15944,10 +15979,10 @@
         <v>80</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>80</v>
+        <v>624</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>105</v>
+        <v>625</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -15958,10 +15993,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>671</v>
+        <v>626</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>671</v>
+        <v>626</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15969,35 +16004,33 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>260</v>
+        <v>618</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>672</v>
+        <v>627</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>673</v>
+        <v>628</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>675</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>80</v>
       </c>
@@ -16021,13 +16054,13 @@
         <v>80</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>80</v>
@@ -16045,34 +16078,34 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>671</v>
+        <v>626</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>103</v>
+        <v>622</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>104</v>
+        <v>623</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>676</v>
+        <v>80</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>355</v>
+        <v>624</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>356</v>
+        <v>629</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>357</v>
+        <v>80</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>80</v>
@@ -16080,10 +16113,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>677</v>
+        <v>630</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>677</v>
+        <v>630</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16097,28 +16130,28 @@
         <v>91</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>678</v>
+        <v>260</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>679</v>
+        <v>631</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>680</v>
+        <v>632</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>681</v>
+        <v>633</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>442</v>
+        <v>634</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -16143,13 +16176,13 @@
         <v>80</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>251</v>
+        <v>175</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>682</v>
+        <v>635</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>80</v>
@@ -16167,7 +16200,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>677</v>
+        <v>630</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -16176,7 +16209,7 @@
         <v>91</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>684</v>
+        <v>103</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>104</v>
@@ -16185,27 +16218,27 @@
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>685</v>
+        <v>637</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>447</v>
+        <v>638</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>448</v>
+        <v>534</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>449</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>686</v>
+        <v>639</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>686</v>
+        <v>639</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16216,10 +16249,10 @@
         <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>80</v>
@@ -16231,16 +16264,16 @@
         <v>260</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>687</v>
+        <v>640</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>688</v>
+        <v>641</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>689</v>
+        <v>642</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>509</v>
+        <v>643</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>80</v>
@@ -16265,13 +16298,13 @@
         <v>80</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>510</v>
+        <v>644</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>511</v>
+        <v>645</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>80</v>
@@ -16289,16 +16322,16 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>686</v>
+        <v>639</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>690</v>
+        <v>103</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>104</v>
@@ -16307,13 +16340,13 @@
         <v>80</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>80</v>
+        <v>637</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>105</v>
+        <v>638</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16324,21 +16357,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>691</v>
+        <v>646</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>691</v>
+        <v>646</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>526</v>
+        <v>80</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>80</v>
@@ -16350,19 +16383,19 @@
         <v>80</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>260</v>
+        <v>647</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>527</v>
+        <v>648</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>528</v>
+        <v>649</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>529</v>
+        <v>650</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>530</v>
+        <v>651</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>80</v>
@@ -16387,13 +16420,13 @@
         <v>80</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>692</v>
+        <v>80</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>531</v>
+        <v>80</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>80</v>
@@ -16411,45 +16444,45 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>691</v>
+        <v>646</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>104</v>
+        <v>652</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>532</v>
+        <v>80</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>533</v>
+        <v>653</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>534</v>
+        <v>654</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>535</v>
+        <v>80</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>693</v>
+        <v>655</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>693</v>
+        <v>655</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16460,7 +16493,7 @@
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>80</v>
@@ -16472,20 +16505,18 @@
         <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>694</v>
+        <v>656</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>695</v>
+        <v>657</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>80</v>
       </c>
@@ -16533,41 +16564,1373 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="Y124" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="AG116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH116" t="s" s="2">
+      <c r="Z124" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G126" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP116" t="s" s="2">
+      <c r="H126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP127" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP116">
+  <autoFilter ref="A1:AP127">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16577,7 +17940,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI115">
+  <conditionalFormatting sqref="A2:AI126">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$116</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4914" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4491" uniqueCount="696">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:22:20+00:00</t>
+    <t>2023-11-28T12:44:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1792,39 +1792,6 @@
   </si>
   <si>
     <t>methodCode</t>
-  </si>
-  <si>
-    <t>Observation.method.id</t>
-  </si>
-  <si>
-    <t>Observation.method.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.method.text</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -2537,7 +2504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP127"/>
+  <dimension ref="A1:AP116"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.58984375" customWidth="true" bestFit="true"/>
@@ -2564,7 +2531,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="109.11328125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="111.65625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -13718,7 +13685,7 @@
         <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>80</v>
@@ -13764,11 +13731,9 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>569</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
         <v>569</v>
       </c>
@@ -13849,15 +13814,17 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>107</v>
+        <v>573</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>108</v>
+        <v>574</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13906,7 +13873,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>110</v>
+        <v>572</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13915,47 +13882,47 @@
         <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>80</v>
+        <v>577</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>80</v>
+        <v>578</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>111</v>
+        <v>579</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>80</v>
+        <v>580</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>80</v>
@@ -13967,16 +13934,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>114</v>
+        <v>582</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>115</v>
+        <v>583</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>116</v>
+        <v>584</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>117</v>
+        <v>585</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14014,57 +13981,57 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>121</v>
+        <v>581</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>122</v>
+        <v>233</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>80</v>
+        <v>586</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>80</v>
+        <v>587</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>105</v>
+        <v>588</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>80</v>
+        <v>589</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14084,22 +14051,22 @@
         <v>80</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>147</v>
+        <v>591</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>279</v>
+        <v>592</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>280</v>
+        <v>593</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>281</v>
+        <v>594</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>282</v>
+        <v>595</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -14148,7 +14115,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>283</v>
+        <v>590</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14160,7 +14127,7 @@
         <v>103</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>104</v>
+        <v>596</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>80</v>
@@ -14169,10 +14136,10 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>284</v>
+        <v>597</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>285</v>
+        <v>598</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14183,10 +14150,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14301,10 +14268,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14421,45 +14388,45 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>80</v>
+        <v>602</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>292</v>
+        <v>603</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>293</v>
+        <v>604</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>294</v>
+        <v>117</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>295</v>
+        <v>215</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>80</v>
@@ -14508,19 +14475,19 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>297</v>
+        <v>605</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>80</v>
@@ -14529,10 +14496,10 @@
         <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>298</v>
+        <v>80</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14543,10 +14510,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14566,19 +14533,19 @@
         <v>80</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>107</v>
+        <v>607</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>302</v>
+        <v>608</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>303</v>
+        <v>609</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>304</v>
+        <v>610</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14628,7 +14595,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>305</v>
+        <v>606</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14637,10 +14604,10 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>103</v>
+        <v>611</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>104</v>
+        <v>612</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>80</v>
@@ -14649,10 +14616,10 @@
         <v>80</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>306</v>
+        <v>613</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>307</v>
+        <v>614</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14663,10 +14630,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>579</v>
+        <v>615</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>579</v>
+        <v>615</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14674,7 +14641,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>91</v>
@@ -14686,23 +14653,21 @@
         <v>80</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>171</v>
+        <v>607</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>310</v>
+        <v>616</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>311</v>
+        <v>617</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>80</v>
       </c>
@@ -14750,7 +14715,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>315</v>
+        <v>615</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14759,10 +14724,10 @@
         <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>103</v>
+        <v>611</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>104</v>
+        <v>612</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>80</v>
@@ -14771,10 +14736,10 @@
         <v>80</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>316</v>
+        <v>613</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>317</v>
+        <v>618</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>80</v>
@@ -14785,10 +14750,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>580</v>
+        <v>619</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>580</v>
+        <v>619</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14808,22 +14773,22 @@
         <v>80</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>107</v>
+        <v>260</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>320</v>
+        <v>620</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>321</v>
+        <v>621</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>312</v>
+        <v>622</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>322</v>
+        <v>623</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>80</v>
@@ -14848,13 +14813,13 @@
         <v>80</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>80</v>
+        <v>624</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>80</v>
+        <v>625</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>80</v>
@@ -14872,7 +14837,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>323</v>
+        <v>619</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14890,13 +14855,13 @@
         <v>80</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>80</v>
+        <v>626</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>324</v>
+        <v>627</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>325</v>
+        <v>534</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>80</v>
@@ -14907,10 +14872,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14921,7 +14886,7 @@
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>80</v>
@@ -14930,22 +14895,22 @@
         <v>80</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>328</v>
+        <v>260</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>329</v>
+        <v>629</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>330</v>
+        <v>630</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>331</v>
+        <v>631</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>332</v>
+        <v>632</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -14970,13 +14935,13 @@
         <v>80</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>80</v>
+        <v>633</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>80</v>
+        <v>634</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>80</v>
@@ -14994,13 +14959,13 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>333</v>
+        <v>628</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>103</v>
@@ -15012,13 +14977,13 @@
         <v>80</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>80</v>
+        <v>626</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>334</v>
+        <v>627</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>335</v>
+        <v>534</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>80</v>
@@ -15029,10 +14994,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>582</v>
+        <v>635</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>582</v>
+        <v>635</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15052,22 +15017,22 @@
         <v>80</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>107</v>
+        <v>636</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>338</v>
+        <v>637</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>339</v>
+        <v>638</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>340</v>
+        <v>639</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>341</v>
+        <v>640</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -15116,7 +15081,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>342</v>
+        <v>635</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -15128,7 +15093,7 @@
         <v>103</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>104</v>
+        <v>641</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>80</v>
@@ -15137,10 +15102,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>343</v>
+        <v>642</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>344</v>
+        <v>643</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -15151,10 +15116,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>583</v>
+        <v>644</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>583</v>
+        <v>644</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15177,16 +15142,16 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>584</v>
+        <v>107</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>585</v>
+        <v>645</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>586</v>
+        <v>646</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>587</v>
+        <v>312</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15236,7 +15201,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>583</v>
+        <v>644</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15248,33 +15213,33 @@
         <v>103</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>233</v>
+        <v>104</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>590</v>
+        <v>647</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>591</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>592</v>
+        <v>648</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>592</v>
+        <v>648</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15285,7 +15250,7 @@
         <v>78</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>80</v>
@@ -15294,19 +15259,19 @@
         <v>80</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>593</v>
+        <v>649</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>594</v>
+        <v>650</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>595</v>
+        <v>651</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>596</v>
+        <v>652</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15356,13 +15321,13 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>592</v>
+        <v>648</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>103</v>
@@ -15374,27 +15339,27 @@
         <v>80</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>597</v>
+        <v>80</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>598</v>
+        <v>653</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>599</v>
+        <v>654</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>600</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>601</v>
+        <v>655</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>601</v>
+        <v>655</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15414,23 +15379,21 @@
         <v>80</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>602</v>
+        <v>656</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>603</v>
+        <v>657</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>604</v>
+        <v>658</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>606</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>80</v>
       </c>
@@ -15478,7 +15441,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>601</v>
+        <v>655</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15490,7 +15453,7 @@
         <v>103</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>607</v>
+        <v>233</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>80</v>
@@ -15499,10 +15462,10 @@
         <v>80</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>608</v>
+        <v>653</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>609</v>
+        <v>660</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15513,10 +15476,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>610</v>
+        <v>661</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>610</v>
+        <v>661</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15527,28 +15490,32 @@
         <v>78</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>107</v>
+        <v>591</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>108</v>
+        <v>662</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>664</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>80</v>
       </c>
@@ -15596,19 +15563,19 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>110</v>
+        <v>661</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>80</v>
+        <v>665</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>80</v>
@@ -15617,10 +15584,10 @@
         <v>80</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>80</v>
+        <v>666</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>111</v>
+        <v>667</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>80</v>
@@ -15631,21 +15598,21 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>611</v>
+        <v>668</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>611</v>
+        <v>668</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>80</v>
@@ -15657,17 +15624,15 @@
         <v>80</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>80</v>
@@ -15704,31 +15669,31 @@
         <v>80</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>80</v>
@@ -15740,7 +15705,7 @@
         <v>80</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>80</v>
@@ -15751,14 +15716,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>612</v>
+        <v>669</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>612</v>
+        <v>669</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>613</v>
+        <v>113</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15771,26 +15736,24 @@
         <v>80</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K110" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>614</v>
+        <v>115</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>615</v>
+        <v>116</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O110" t="s" s="2">
-        <v>215</v>
-      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>80</v>
       </c>
@@ -15826,19 +15789,19 @@
         <v>80</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>616</v>
+        <v>121</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15873,44 +15836,46 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>617</v>
+        <v>670</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>617</v>
+        <v>670</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>80</v>
+        <v>602</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>618</v>
+        <v>114</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O111" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>80</v>
       </c>
@@ -15958,19 +15923,19 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>622</v>
+        <v>103</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>623</v>
+        <v>122</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>80</v>
@@ -15979,10 +15944,10 @@
         <v>80</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>624</v>
+        <v>80</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>625</v>
+        <v>105</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -15993,10 +15958,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>626</v>
+        <v>671</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>626</v>
+        <v>671</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16004,33 +15969,35 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>618</v>
+        <v>260</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>627</v>
+        <v>672</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>628</v>
+        <v>673</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O112" s="2"/>
+        <v>674</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>675</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>80</v>
       </c>
@@ -16054,13 +16021,13 @@
         <v>80</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>80</v>
@@ -16078,34 +16045,34 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>626</v>
+        <v>671</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>622</v>
+        <v>103</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>623</v>
+        <v>104</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>80</v>
+        <v>676</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>624</v>
+        <v>355</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>629</v>
+        <v>356</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>80</v>
@@ -16113,10 +16080,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16130,28 +16097,28 @@
         <v>91</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>260</v>
+        <v>678</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>631</v>
+        <v>679</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>632</v>
+        <v>680</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>633</v>
+        <v>681</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>634</v>
+        <v>442</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -16176,13 +16143,13 @@
         <v>80</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>175</v>
+        <v>251</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>636</v>
+        <v>683</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>80</v>
@@ -16200,7 +16167,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -16209,7 +16176,7 @@
         <v>91</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>103</v>
+        <v>684</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>104</v>
@@ -16218,27 +16185,27 @@
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>637</v>
+        <v>685</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>638</v>
+        <v>447</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>534</v>
+        <v>448</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16249,10 +16216,10 @@
         <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>80</v>
@@ -16264,16 +16231,16 @@
         <v>260</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>640</v>
+        <v>687</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>641</v>
+        <v>688</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>642</v>
+        <v>689</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>643</v>
+        <v>509</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>80</v>
@@ -16298,13 +16265,13 @@
         <v>80</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>644</v>
+        <v>510</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>645</v>
+        <v>511</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>80</v>
@@ -16322,16 +16289,16 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>103</v>
+        <v>690</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>104</v>
@@ -16340,13 +16307,13 @@
         <v>80</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>637</v>
+        <v>80</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>638</v>
+        <v>105</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16357,21 +16324,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>646</v>
+        <v>691</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>646</v>
+        <v>691</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>80</v>
+        <v>526</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>80</v>
@@ -16383,19 +16350,19 @@
         <v>80</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>647</v>
+        <v>260</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>648</v>
+        <v>527</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>649</v>
+        <v>528</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>650</v>
+        <v>529</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>651</v>
+        <v>530</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>80</v>
@@ -16420,13 +16387,13 @@
         <v>80</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>80</v>
+        <v>692</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>80</v>
+        <v>531</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>80</v>
@@ -16444,45 +16411,45 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>646</v>
+        <v>691</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>652</v>
+        <v>104</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>80</v>
+        <v>532</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>653</v>
+        <v>533</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>654</v>
+        <v>534</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>80</v>
+        <v>535</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>655</v>
+        <v>693</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>655</v>
+        <v>693</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16493,7 +16460,7 @@
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>80</v>
@@ -16505,18 +16472,20 @@
         <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>656</v>
+        <v>694</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>657</v>
+        <v>695</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>80</v>
       </c>
@@ -16564,19 +16533,19 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>655</v>
+        <v>693</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>80</v>
@@ -16585,1352 +16554,20 @@
         <v>80</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>624</v>
+        <v>597</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>658</v>
+        <v>598</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP119" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="P124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="P127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP127" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP127">
+  <autoFilter ref="A1:AP116">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17940,7 +16577,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI126">
+  <conditionalFormatting sqref="A2:AI115">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:44:29+00:00</t>
+    <t>2023-11-28T13:07:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:07:26+00:00</t>
+    <t>2023-11-28T13:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1829,13 +1829,12 @@
 </t>
   </si>
   <si>
-    <t>Dispositif utilisé pour l'observation</t>
-  </si>
-  <si>
     <t>Dispositif utilisé pour l'observation
 Si la mesure a été faite par un objet connecté (Profil PhdDevice)
-=&gt;cette référence est obligatoire
-http://hl7.org/fhir/uv/phd/StructureDefinition/PhdDevice</t>
+, cette référence est obligatoire</t>
+  </si>
+  <si>
+    <t>The device used to generate the observation data.</t>
   </si>
   <si>
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
@@ -13925,7 +13924,7 @@
         <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:18:47+00:00</t>
+    <t>2023-11-28T13:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:27:45+00:00</t>
+    <t>2023-11-28T13:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:42:11+00:00</t>
+    <t>2023-12-08T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T10:33:05+00:00</t>
+    <t>2023-12-29T10:04:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T10:04:05+00:00</t>
+    <t>2024-02-01T10:35:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T10:35:02+00:00</t>
+    <t>2024-02-01T13:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:55:30+00:00</t>
+    <t>2024-02-01T13:56:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:56:11+00:00</t>
+    <t>2024-02-01T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T14:29:51+00:00</t>
+    <t>2024-02-01T16:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T16:04:25+00:00</t>
+    <t>2024-02-05T14:48:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T14:48:49+00:00</t>
+    <t>2024-02-12T14:46:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:46:58+00:00</t>
+    <t>2024-02-12T14:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:53:29+00:00</t>
+    <t>2024-04-08T08:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
